--- a/Arquivos/Pesquisa_Operacional_28_10_2026.xlsx
+++ b/Arquivos/Pesquisa_Operacional_28_10_2026.xlsx
@@ -8,109 +8,146 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA2C0D8-46D8-45E0-87D0-ADECBC8F64D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A01CF2-38B4-4D9E-8B8C-93A58A35A342}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{8D6C0FA3-C012-4463-B83B-7B6D56B3562A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="3" xr2:uid="{8D6C0FA3-C012-4463-B83B-7B6D56B3562A}"/>
   </bookViews>
   <sheets>
     <sheet name="Ex1- De Transbordo" sheetId="7" r:id="rId1"/>
     <sheet name="Ex2- De Problemas de Transporte" sheetId="8" r:id="rId2"/>
-    <sheet name="EX3" sheetId="9" r:id="rId3"/>
+    <sheet name="Ex3" sheetId="9" r:id="rId3"/>
+    <sheet name="Ex4" sheetId="10" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'Ex1- De Transbordo'!$B$5:$J$6</definedName>
     <definedName name="solver_adj" localSheetId="1" hidden="1">'Ex2- De Problemas de Transporte'!$B$5:$Q$5</definedName>
-    <definedName name="solver_adj" localSheetId="2" hidden="1">'EX3'!$B$3:$J$3</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">'Ex3'!$B$3:$J$3</definedName>
+    <definedName name="solver_adj" localSheetId="3" hidden="1">'Ex4'!$B$2:$M$2</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'Ex1- De Transbordo'!$L$9:$L$10</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">'Ex2- De Problemas de Transporte'!$R$10:$R$17</definedName>
-    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'EX3'!$K$7:$K$12</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'Ex3'!$K$7:$K$12</definedName>
+    <definedName name="solver_lhs1" localSheetId="3" hidden="1">'Ex4'!$N$10:$N$13</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">'Ex1- De Transbordo'!$L$9:$L$14</definedName>
+    <definedName name="solver_lhs2" localSheetId="3" hidden="1">'Ex4'!$N$6:$N$8</definedName>
+    <definedName name="solver_lhs3" localSheetId="3" hidden="1">'Ex4'!$N$9</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="3" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="3" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'Ex1- De Transbordo'!$M$6</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">'Ex2- De Problemas de Transporte'!$S$7</definedName>
-    <definedName name="solver_opt" localSheetId="2" hidden="1">'EX3'!$M$4</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">'Ex3'!$M$4</definedName>
+    <definedName name="solver_opt" localSheetId="3" hidden="1">'Ex4'!$P$2</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="3" hidden="1">3</definedName>
+    <definedName name="solver_rel3" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">'Ex1- De Transbordo'!$M$9:$M$10</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">'Ex2- De Problemas de Transporte'!$S$10:$S$17</definedName>
-    <definedName name="solver_rhs1" localSheetId="2" hidden="1">'EX3'!$L$7:$L$12</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">'Ex3'!$L$7:$L$12</definedName>
+    <definedName name="solver_rhs1" localSheetId="3" hidden="1">'Ex4'!$O$10:$O$13</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">'Ex1- De Transbordo'!$M$9:$M$14</definedName>
+    <definedName name="solver_rhs2" localSheetId="3" hidden="1">'Ex4'!$O$6:$O$8</definedName>
+    <definedName name="solver_rhs3" localSheetId="3" hidden="1">'Ex4'!$O$9</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="3" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="3" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -214,7 +251,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="87">
   <si>
     <t>X11</t>
   </si>
@@ -420,6 +457,72 @@
   </si>
   <si>
     <t>CAP</t>
+  </si>
+  <si>
+    <t>M1 OP1</t>
+  </si>
+  <si>
+    <t>M1 OP2</t>
+  </si>
+  <si>
+    <t>M1 OP3</t>
+  </si>
+  <si>
+    <t>M1 OP4</t>
+  </si>
+  <si>
+    <t>M2 OP1</t>
+  </si>
+  <si>
+    <t>M2 OP2</t>
+  </si>
+  <si>
+    <t>M2 OP3</t>
+  </si>
+  <si>
+    <t>M2 OP4</t>
+  </si>
+  <si>
+    <t>M3 OP1</t>
+  </si>
+  <si>
+    <t>M3 OP2</t>
+  </si>
+  <si>
+    <t>M3 OP3</t>
+  </si>
+  <si>
+    <t>M3 OP4</t>
+  </si>
+  <si>
+    <t>OPS CUSTO</t>
+  </si>
+  <si>
+    <t>RESTRIÇÃO</t>
+  </si>
+  <si>
+    <t>TEMPO M1</t>
+  </si>
+  <si>
+    <t>TEMPO M2</t>
+  </si>
+  <si>
+    <t>TEMPO M3</t>
+  </si>
+  <si>
+    <t>TTOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OP1 </t>
+  </si>
+  <si>
+    <t>OP2</t>
+  </si>
+  <si>
+    <t>OP3</t>
+  </si>
+  <si>
+    <t>OP4</t>
   </si>
 </sst>
 </file>
@@ -480,7 +583,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -514,15 +617,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -530,6 +647,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -963,6 +1081,143 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>153870</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>54060</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7586273F-1862-45A7-A225-B79D1C276BCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10934700" y="142875"/>
+          <a:ext cx="7011870" cy="3911685"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>412369</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>172180</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CFB5A8F-7E6D-42C7-AD25-D01B9F9918BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="2800350"/>
+          <a:ext cx="5632069" cy="4229830"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>65476</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>354568</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>124523</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDCD8133-058D-4C40-BF4A-2CB4888E9E20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5962650" y="3875476"/>
+          <a:ext cx="11879818" cy="3869047"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
@@ -1273,12 +1528,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1560,10 +1815,10 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="M16" s="5" t="s">
+      <c r="M16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N16" s="5"/>
+      <c r="N16" s="6"/>
     </row>
     <row r="17" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
@@ -1572,8 +1827,8 @@
       <c r="F17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
@@ -1665,40 +1920,40 @@
       <c r="E4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="7" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1860,7 +2115,7 @@
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
-      <c r="R10" s="7">
+      <c r="R10" s="8">
         <f>SUMPRODUCT($B$5:$Q$5,B10:Q10)</f>
         <v>1</v>
       </c>
@@ -1896,7 +2151,7 @@
       </c>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
-      <c r="R11" s="7">
+      <c r="R11" s="8">
         <f t="shared" ref="R11:R17" si="0">SUMPRODUCT($B$5:$Q$5,B11:Q11)</f>
         <v>1</v>
       </c>
@@ -1932,7 +2187,7 @@
         <v>1</v>
       </c>
       <c r="Q12" s="2"/>
-      <c r="R12" s="7">
+      <c r="R12" s="8">
         <f>SUMPRODUCT($B$5:$Q$5,B12:Q12)</f>
         <v>1</v>
       </c>
@@ -1966,7 +2221,7 @@
       <c r="Q13" s="2">
         <v>1</v>
       </c>
-      <c r="R13" s="7">
+      <c r="R13" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2004,7 +2259,7 @@
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
-      <c r="R14" s="7">
+      <c r="R14" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2040,7 +2295,7 @@
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
-      <c r="R15" s="7">
+      <c r="R15" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2076,7 +2331,7 @@
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
-      <c r="R16" s="7">
+      <c r="R16" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2112,7 +2367,7 @@
       <c r="Q17" s="2">
         <v>1</v>
       </c>
-      <c r="R17" s="7">
+      <c r="R17" s="8">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2165,31 +2420,31 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="8">
-        <v>0</v>
-      </c>
-      <c r="C3" s="8">
-        <v>1</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0</v>
-      </c>
-      <c r="E3" s="8">
-        <v>1</v>
-      </c>
-      <c r="F3" s="8">
-        <v>0</v>
-      </c>
-      <c r="G3" s="8">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8">
-        <v>0</v>
-      </c>
-      <c r="I3" s="8">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8">
+      <c r="B3" s="9">
+        <v>0</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0</v>
+      </c>
+      <c r="E3" s="9">
+        <v>1</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0</v>
+      </c>
+      <c r="G3" s="9">
+        <v>0</v>
+      </c>
+      <c r="H3" s="9">
+        <v>0</v>
+      </c>
+      <c r="I3" s="9">
+        <v>0</v>
+      </c>
+      <c r="J3" s="9">
         <v>1</v>
       </c>
     </row>
@@ -2372,4 +2627,432 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A2066CF-B02A-4DA2-81AD-9FA46C579E2D}">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3">
+        <v>1</v>
+      </c>
+      <c r="L2" s="3">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2" s="3">
+        <f>SUMPRODUCT(B2:M2,B3:M3)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="2">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2">
+        <v>61</v>
+      </c>
+      <c r="D3" s="2">
+        <v>33</v>
+      </c>
+      <c r="E3" s="2">
+        <v>94</v>
+      </c>
+      <c r="F3" s="2">
+        <v>21</v>
+      </c>
+      <c r="G3" s="2">
+        <v>58</v>
+      </c>
+      <c r="H3" s="2">
+        <v>40</v>
+      </c>
+      <c r="I3" s="2">
+        <v>86</v>
+      </c>
+      <c r="J3" s="2">
+        <v>19</v>
+      </c>
+      <c r="K3" s="2">
+        <v>68</v>
+      </c>
+      <c r="L3" s="2">
+        <v>27</v>
+      </c>
+      <c r="M3" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="2">
+        <v>32</v>
+      </c>
+      <c r="C6" s="2">
+        <v>57</v>
+      </c>
+      <c r="D6" s="2">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2">
+        <f>SUMPRODUCT($B$2:$M$2,B6:M6)</f>
+        <v>32</v>
+      </c>
+      <c r="O6" s="2">
+        <f>32+57+17+56</f>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2">
+        <f t="shared" ref="N7:N13" si="0">SUMPRODUCT($B$2:$M$2,B7:M7)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <f>27+50+22+48</f>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O8" s="2">
+        <f>18+45+13+60</f>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O9" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2">
+        <f>SUMPRODUCT($B$2:$M$2,B10:M10)</f>
+        <v>1</v>
+      </c>
+      <c r="O10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2">
+        <v>1</v>
+      </c>
+      <c r="N13" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Arquivos/Pesquisa_Operacional_28_10_2026.xlsx
+++ b/Arquivos/Pesquisa_Operacional_28_10_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A01CF2-38B4-4D9E-8B8C-93A58A35A342}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65FDBA2F-666F-422F-8F76-ABE3E53FB75E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="3" xr2:uid="{8D6C0FA3-C012-4463-B83B-7B6D56B3562A}"/>
   </bookViews>
@@ -46,10 +46,10 @@
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'Ex1- De Transbordo'!$L$9:$L$10</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">'Ex2- De Problemas de Transporte'!$R$10:$R$17</definedName>
     <definedName name="solver_lhs1" localSheetId="2" hidden="1">'Ex3'!$K$7:$K$12</definedName>
-    <definedName name="solver_lhs1" localSheetId="3" hidden="1">'Ex4'!$N$10:$N$13</definedName>
+    <definedName name="solver_lhs1" localSheetId="3" hidden="1">'Ex4'!$N$13:$N$15</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">'Ex1- De Transbordo'!$L$9:$L$14</definedName>
     <definedName name="solver_lhs2" localSheetId="3" hidden="1">'Ex4'!$N$6:$N$8</definedName>
-    <definedName name="solver_lhs3" localSheetId="3" hidden="1">'Ex4'!$N$9</definedName>
+    <definedName name="solver_lhs3" localSheetId="3" hidden="1">'Ex4'!$N$9:$N$12</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
@@ -97,17 +97,17 @@
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">2</definedName>
-    <definedName name="solver_rel1" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_rel2" localSheetId="3" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">'Ex1- De Transbordo'!$M$9:$M$10</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">'Ex2- De Problemas de Transporte'!$S$10:$S$17</definedName>
     <definedName name="solver_rhs1" localSheetId="2" hidden="1">'Ex3'!$L$7:$L$12</definedName>
-    <definedName name="solver_rhs1" localSheetId="3" hidden="1">'Ex4'!$O$10:$O$13</definedName>
+    <definedName name="solver_rhs1" localSheetId="3" hidden="1">'Ex4'!$O$13:$O$15</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">'Ex1- De Transbordo'!$M$9:$M$14</definedName>
     <definedName name="solver_rhs2" localSheetId="3" hidden="1">'Ex4'!$O$6:$O$8</definedName>
-    <definedName name="solver_rhs3" localSheetId="3" hidden="1">'Ex4'!$O$9</definedName>
+    <definedName name="solver_rhs3" localSheetId="3" hidden="1">'Ex4'!$O$9:$O$12</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
@@ -251,7 +251,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="90">
   <si>
     <t>X11</t>
   </si>
@@ -510,9 +510,6 @@
     <t>TEMPO M3</t>
   </si>
   <si>
-    <t>TTOTAL</t>
-  </si>
-  <si>
     <t xml:space="preserve">OP1 </t>
   </si>
   <si>
@@ -523,6 +520,18 @@
   </si>
   <si>
     <t>OP4</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>&gt;=</t>
   </si>
 </sst>
 </file>
@@ -1129,16 +1138,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>412369</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>172180</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>440944</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>19780</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1161,7 +1170,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="76200" y="2800350"/>
+          <a:off x="11077575" y="4362450"/>
           <a:ext cx="5632069" cy="4229830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1173,23 +1182,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>65476</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>354568</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>124523</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>11184</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>143577</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagem 3">
+        <xdr:cNvPr id="6" name="Imagem 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDCD8133-058D-4C40-BF4A-2CB4888E9E20}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7902D77B-ED77-4E49-9C3C-93C4B2703F91}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1205,8 +1214,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5962650" y="3875476"/>
-          <a:ext cx="11879818" cy="3869047"/>
+          <a:off x="352425" y="2981325"/>
+          <a:ext cx="3735459" cy="3829752"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2631,7 +2640,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A2066CF-B02A-4DA2-81AD-9FA46C579E2D}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -2692,32 +2701,32 @@
         <v>0</v>
       </c>
       <c r="G2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3">
         <v>0</v>
       </c>
       <c r="I2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
       </c>
       <c r="K2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3">
         <v>1</v>
       </c>
       <c r="M2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="P2" s="3">
         <f>SUMPRODUCT(B2:M2,B3:M3)</f>
-        <v>200</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -2798,7 +2807,7 @@
         <v>17</v>
       </c>
       <c r="E6" s="2">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -2813,8 +2822,7 @@
         <v>32</v>
       </c>
       <c r="O6" s="2">
-        <f>32+57+17+56</f>
-        <v>162</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -2826,28 +2834,27 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G7" s="2">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H7" s="2">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="I7" s="2">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2">
-        <f t="shared" ref="N7:N13" si="0">SUMPRODUCT($B$2:$M$2,B7:M7)</f>
-        <v>0</v>
+        <f t="shared" ref="N7:N15" si="0">SUMPRODUCT($B$2:$M$2,B7:M7)</f>
+        <v>98</v>
       </c>
       <c r="O7" s="2">
-        <f>27+50+22+48</f>
-        <v>147</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -2863,24 +2870,23 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K8" s="2">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="L8" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M8" s="2">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="N8" s="2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O8" s="2">
-        <f>18+45+13+60</f>
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -2890,71 +2896,53 @@
       <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
       <c r="J9" s="2">
         <v>1</v>
       </c>
-      <c r="K9" s="2">
-        <v>1</v>
-      </c>
-      <c r="L9" s="2">
-        <v>1</v>
-      </c>
-      <c r="M9" s="2">
-        <v>1</v>
-      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
       <c r="N9" s="2">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>SUMPRODUCT($B$2:$M$2,B9:M9)</f>
+        <v>1</v>
       </c>
       <c r="O9" s="2">
-        <v>120</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="2">
-        <v>1</v>
-      </c>
-      <c r="K10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2">
-        <f>SUMPRODUCT($B$2:$M$2,B10:M10)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="O10" s="2">
@@ -2966,22 +2954,22 @@
         <v>84</v>
       </c>
       <c r="B11" s="2"/>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="2">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="2">
-        <v>1</v>
-      </c>
-      <c r="L11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2">
+        <v>1</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2">
         <f t="shared" si="0"/>
@@ -2997,22 +2985,22 @@
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="2">
-        <v>1</v>
-      </c>
-      <c r="I12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-      <c r="L12" s="2">
-        <v>1</v>
-      </c>
-      <c r="M12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2">
+        <v>1</v>
+      </c>
       <c r="N12" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -3022,32 +3010,77 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2">
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
         <v>1</v>
       </c>
       <c r="N13" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O13" s="2">
+      <c r="O13" s="7">
+        <v>1</v>
+      </c>
+      <c r="P13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O14" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O15" s="7">
         <v>1</v>
       </c>
     </row>
